--- a/academias/Lengua y Comunicación - Estadisticos 20241.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20241.xlsx
@@ -1574,25 +1574,25 @@
         <v>33</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>9.1</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1609,25 +1609,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1644,25 +1644,25 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1679,25 +1679,25 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>15.8</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1714,25 +1714,25 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1746,25 +1746,25 @@
         <v>119</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F7">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>11.8</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J7">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1781,25 +1781,25 @@
         <v>39</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1816,25 +1816,25 @@
         <v>34</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>91.2</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1851,25 +1851,25 @@
         <v>33</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>18.2</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1886,25 +1886,25 @@
         <v>23</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1921,25 +1921,25 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1953,25 +1953,25 @@
         <v>148</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="F13">
-        <v>148</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>6.1</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1988,25 +1988,25 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>79.2</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>20.8</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2023,25 +2023,25 @@
         <v>36</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F15">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>11.1</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2058,25 +2058,25 @@
         <v>28</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F16">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J16">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2093,25 +2093,25 @@
         <v>35</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>11.4</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J17">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2128,25 +2128,25 @@
         <v>24</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>70.8</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>29.2</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J18">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2163,25 +2163,25 @@
         <v>37</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>2.7</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J19">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2195,25 +2195,25 @@
         <v>184</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="F20">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J20">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2498,25 +2498,25 @@
         <v>663</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="F29">
-        <v>663</v>
+        <v>258</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>61.1</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>38.9</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J29">
-        <v>663</v>
+        <v>212</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2584,19 +2584,19 @@
         <v>33</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>84.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>15.2</v>
+        <v>9.1</v>
       </c>
       <c r="I2" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2619,19 +2619,19 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>61.9</v>
+        <v>85.7</v>
       </c>
       <c r="H3" s="1">
-        <v>38.1</v>
+        <v>14.3</v>
       </c>
       <c r="I3" s="2">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2654,19 +2654,19 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H4" s="1">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="I4" s="2">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2689,19 +2689,19 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>68.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="H5" s="1">
-        <v>31.6</v>
+        <v>15.8</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2724,19 +2724,19 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>81</v>
+        <v>95.2</v>
       </c>
       <c r="H6" s="1">
-        <v>19</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2756,19 +2756,19 @@
         <v>119</v>
       </c>
       <c r="E7">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>72.3</v>
+        <v>88.2</v>
       </c>
       <c r="H7" s="1">
-        <v>27.7</v>
+        <v>11.8</v>
       </c>
       <c r="I7" s="2">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2791,19 +2791,19 @@
         <v>39</v>
       </c>
       <c r="E8">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>89.7</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2826,16 +2826,16 @@
         <v>34</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>88.2</v>
+        <v>91.2</v>
       </c>
       <c r="H9" s="1">
-        <v>11.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I9" s="2">
         <v>7.7</v>
@@ -2861,19 +2861,19 @@
         <v>33</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>75.8</v>
+        <v>81.8</v>
       </c>
       <c r="H10" s="1">
-        <v>24.2</v>
+        <v>18.2</v>
       </c>
       <c r="I10" s="2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2896,19 +2896,19 @@
         <v>23</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>69.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>30.4</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2931,19 +2931,19 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2963,19 +2963,19 @@
         <v>148</v>
       </c>
       <c r="E13">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>83.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>16.2</v>
+        <v>6.1</v>
       </c>
       <c r="I13" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3010,7 +3010,7 @@
         <v>20.8</v>
       </c>
       <c r="I14" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>36</v>
       </c>
       <c r="E15">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>91.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>8.300000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="I15" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         <v>7.1</v>
       </c>
       <c r="I16" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>11.4</v>
       </c>
       <c r="I17" s="2">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         <v>29.2</v>
       </c>
       <c r="I18" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3173,19 +3173,19 @@
         <v>37</v>
       </c>
       <c r="E19">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>91.90000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="H19" s="1">
-        <v>8.1</v>
+        <v>2.7</v>
       </c>
       <c r="I19" s="2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3205,19 +3205,19 @@
         <v>184</v>
       </c>
       <c r="E20">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" s="1">
-        <v>87</v>
+        <v>87.5</v>
       </c>
       <c r="H20" s="1">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="I20" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3508,19 +3508,19 @@
         <v>663</v>
       </c>
       <c r="E29">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="F29">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="G29" s="1">
-        <v>85.5</v>
+        <v>90.8</v>
       </c>
       <c r="H29" s="1">
-        <v>14.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I29" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J29">
         <v>0</v>

--- a/academias/Lengua y Comunicación - Estadisticos 20241.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20241.xlsx
@@ -51,12 +51,12 @@
     <t>por_blancos</t>
   </si>
   <si>
+    <t>Breniz Camarillo Lysette</t>
+  </si>
+  <si>
     <t>Hernández López Elizabeth</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
@@ -69,15 +69,30 @@
     <t>Lengua y comunicación I</t>
   </si>
   <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
     <t>Lengua y comunicación III</t>
   </si>
   <si>
-    <t>Totales Docente</t>
-  </si>
-  <si>
     <t>Totales Generales</t>
   </si>
   <si>
+    <t>1AV</t>
+  </si>
+  <si>
+    <t>1BV</t>
+  </si>
+  <si>
+    <t>1CV</t>
+  </si>
+  <si>
+    <t>1DV</t>
+  </si>
+  <si>
+    <t>1EV</t>
+  </si>
+  <si>
     <t>1FM</t>
   </si>
   <si>
@@ -91,21 +106,6 @@
   </si>
   <si>
     <t>3ARHV</t>
-  </si>
-  <si>
-    <t>1AV</t>
-  </si>
-  <si>
-    <t>1BV</t>
-  </si>
-  <si>
-    <t>1CV</t>
-  </si>
-  <si>
-    <t>1DV</t>
-  </si>
-  <si>
-    <t>1EV</t>
   </si>
   <si>
     <t>3AEM</t>
@@ -561,22 +561,22 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>84.8</v>
+        <v>89.7</v>
       </c>
       <c r="H2" s="1">
-        <v>15.2</v>
+        <v>10.3</v>
       </c>
       <c r="I2" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -590,28 +590,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>61.9</v>
+        <v>88.2</v>
       </c>
       <c r="H3" s="1">
-        <v>38.1</v>
+        <v>11.8</v>
       </c>
       <c r="I3" s="2">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -625,28 +625,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
       <c r="D4">
+        <v>33</v>
+      </c>
+      <c r="E4">
         <v>25</v>
       </c>
-      <c r="E4">
-        <v>15</v>
-      </c>
       <c r="F4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>60</v>
+        <v>75.8</v>
       </c>
       <c r="H4" s="1">
-        <v>40</v>
+        <v>24.2</v>
       </c>
       <c r="I4" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -660,28 +660,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>68.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>31.6</v>
+        <v>30.4</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -695,28 +695,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>81</v>
+        <v>94.7</v>
       </c>
       <c r="H6" s="1">
-        <v>19</v>
+        <v>5.3</v>
       </c>
       <c r="I6" s="2">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -730,25 +730,25 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="E7">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G7" s="1">
-        <v>72.3</v>
+        <v>83.8</v>
       </c>
       <c r="H7" s="1">
-        <v>27.7</v>
+        <v>16.2</v>
       </c>
       <c r="I7" s="2">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -768,22 +768,22 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E8">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>89.7</v>
+        <v>84.8</v>
       </c>
       <c r="H8" s="1">
-        <v>10.3</v>
+        <v>15.2</v>
       </c>
       <c r="I8" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -797,28 +797,28 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>88.2</v>
+        <v>61.9</v>
       </c>
       <c r="H9" s="1">
-        <v>11.8</v>
+        <v>38.1</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -832,28 +832,28 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>75.8</v>
+        <v>60</v>
       </c>
       <c r="H10" s="1">
-        <v>24.2</v>
+        <v>40</v>
       </c>
       <c r="I10" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -867,28 +867,28 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
       </c>
       <c r="D11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>69.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>30.4</v>
+        <v>31.6</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -902,28 +902,28 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
         <v>29</v>
       </c>
       <c r="D12">
+        <v>21</v>
+      </c>
+      <c r="E12">
+        <v>17</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1">
+        <v>81</v>
+      </c>
+      <c r="H12" s="1">
         <v>19</v>
       </c>
-      <c r="E12">
-        <v>18</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
-        <v>94.7</v>
-      </c>
-      <c r="H12" s="1">
-        <v>5.3</v>
-      </c>
       <c r="I12" s="2">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -937,25 +937,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="E13">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G13" s="1">
-        <v>83.8</v>
+        <v>72.3</v>
       </c>
       <c r="H13" s="1">
-        <v>16.2</v>
+        <v>27.7</v>
       </c>
       <c r="I13" s="2">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -969,7 +969,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>30</v>
@@ -1004,7 +1004,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -1039,7 +1039,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
@@ -1074,7 +1074,7 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
@@ -1109,7 +1109,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
         <v>34</v>
@@ -1144,7 +1144,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>35</v>
@@ -1179,7 +1179,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20">
         <v>184</v>
@@ -1211,7 +1211,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
@@ -1246,7 +1246,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22">
         <v>10</v>
@@ -1453,7 +1453,7 @@
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D28">
         <v>202</v>
@@ -1571,22 +1571,22 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1600,28 +1600,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>85.7</v>
+        <v>91.2</v>
       </c>
       <c r="H3" s="1">
-        <v>14.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3" s="2">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1635,28 +1635,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>84</v>
+        <v>81.8</v>
       </c>
       <c r="H4" s="1">
-        <v>16</v>
+        <v>18.2</v>
       </c>
       <c r="I4" s="2">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1670,28 +1670,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1705,28 +1705,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1740,25 +1740,25 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="E7">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>88.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>11.8</v>
+        <v>6.1</v>
       </c>
       <c r="I7" s="2">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1778,22 +1778,22 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E8">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I8" s="2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1807,28 +1807,28 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F9">
         <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>91.2</v>
+        <v>85.7</v>
       </c>
       <c r="H9" s="1">
-        <v>8.800000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="I9" s="2">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1842,28 +1842,28 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>81.8</v>
+        <v>84</v>
       </c>
       <c r="H10" s="1">
-        <v>18.2</v>
+        <v>16</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1877,28 +1877,28 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
       </c>
       <c r="D11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="I11" s="2">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1912,28 +1912,28 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
         <v>29</v>
       </c>
       <c r="D12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I12" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1947,25 +1947,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="E13">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1">
-        <v>93.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H13" s="1">
-        <v>6.1</v>
+        <v>11.8</v>
       </c>
       <c r="I13" s="2">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>30</v>
@@ -2014,7 +2014,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -2049,7 +2049,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
@@ -2084,7 +2084,7 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
@@ -2119,7 +2119,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
         <v>34</v>
@@ -2154,7 +2154,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>35</v>
@@ -2189,7 +2189,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20">
         <v>184</v>
@@ -2221,7 +2221,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
@@ -2230,25 +2230,25 @@
         <v>10</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="J21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2256,31 +2256,31 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22">
         <v>10</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="J22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2297,25 +2297,25 @@
         <v>40</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F23">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J23">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2332,25 +2332,25 @@
         <v>41</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F24">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>14.6</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2367,25 +2367,25 @@
         <v>48</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F25">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>6.2</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2402,25 +2402,25 @@
         <v>36</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F26">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>5.6</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J26">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2437,25 +2437,25 @@
         <v>37</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F27">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>8.1</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J27">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2463,31 +2463,31 @@
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D28">
         <v>202</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="F28">
-        <v>202</v>
+        <v>18</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>8.9</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J28">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2498,25 +2498,25 @@
         <v>663</v>
       </c>
       <c r="E29">
-        <v>405</v>
+        <v>599</v>
       </c>
       <c r="F29">
-        <v>258</v>
+        <v>64</v>
       </c>
       <c r="G29" s="1">
-        <v>61.1</v>
+        <v>90.3</v>
       </c>
       <c r="H29" s="1">
-        <v>38.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I29" s="2">
-        <v>5.8</v>
+        <v>7.9</v>
       </c>
       <c r="J29">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2581,22 +2581,22 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2610,28 +2610,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>85.7</v>
+        <v>91.2</v>
       </c>
       <c r="H3" s="1">
-        <v>14.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2645,28 +2645,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>84</v>
+        <v>81.8</v>
       </c>
       <c r="H4" s="1">
-        <v>16</v>
+        <v>18.2</v>
       </c>
       <c r="I4" s="2">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2680,28 +2680,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2715,28 +2715,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2750,25 +2750,25 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="E7">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>88.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>11.8</v>
+        <v>6.1</v>
       </c>
       <c r="I7" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2788,22 +2788,22 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E8">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2817,28 +2817,28 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F9">
         <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>91.2</v>
+        <v>85.7</v>
       </c>
       <c r="H9" s="1">
-        <v>8.800000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2852,28 +2852,28 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>81.8</v>
+        <v>84</v>
       </c>
       <c r="H10" s="1">
-        <v>18.2</v>
+        <v>16</v>
       </c>
       <c r="I10" s="2">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2887,28 +2887,28 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
       </c>
       <c r="D11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="I11" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2922,28 +2922,28 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
         <v>29</v>
       </c>
       <c r="D12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I12" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2957,25 +2957,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="E13">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1">
-        <v>93.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H13" s="1">
-        <v>6.1</v>
+        <v>11.8</v>
       </c>
       <c r="I13" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>30</v>
@@ -3024,7 +3024,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -3059,7 +3059,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
@@ -3094,7 +3094,7 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
@@ -3129,7 +3129,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
         <v>34</v>
@@ -3164,7 +3164,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>35</v>
@@ -3199,7 +3199,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20">
         <v>184</v>
@@ -3231,7 +3231,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3266,7 +3266,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22">
         <v>10</v>
@@ -3284,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3307,19 +3307,19 @@
         <v>40</v>
       </c>
       <c r="E23">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1">
-        <v>92.5</v>
+        <v>90</v>
       </c>
       <c r="H23" s="1">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I23" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3342,19 +3342,19 @@
         <v>41</v>
       </c>
       <c r="E24">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" s="1">
-        <v>87.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>12.2</v>
+        <v>14.6</v>
       </c>
       <c r="I24" s="2">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3377,19 +3377,19 @@
         <v>48</v>
       </c>
       <c r="E25">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>91.7</v>
+        <v>93.8</v>
       </c>
       <c r="H25" s="1">
-        <v>8.300000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="I25" s="2">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3412,19 +3412,19 @@
         <v>36</v>
       </c>
       <c r="E26">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I26" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>8.1</v>
       </c>
       <c r="I27" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3473,25 +3473,25 @@
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D28">
         <v>202</v>
       </c>
       <c r="E28">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G28" s="1">
-        <v>92.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="I28" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3508,19 +3508,19 @@
         <v>663</v>
       </c>
       <c r="E29">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="F29">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G29" s="1">
-        <v>90.8</v>
+        <v>90.3</v>
       </c>
       <c r="H29" s="1">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I29" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J29">
         <v>0</v>

--- a/academias/Lengua y Comunicación - Estadisticos 20241.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20241.xlsx
@@ -2943,7 +2943,7 @@
         <v>4.8</v>
       </c>
       <c r="I12" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Lengua y Comunicación - Estadisticos 20241.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20241.xlsx
@@ -2584,19 +2584,19 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>89.7</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="I2" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2619,19 +2619,19 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>91.2</v>
+        <v>88.2</v>
       </c>
       <c r="H3" s="1">
-        <v>8.800000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="I3" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2654,19 +2654,19 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>81.8</v>
+        <v>72.7</v>
       </c>
       <c r="H4" s="1">
-        <v>18.2</v>
+        <v>27.3</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2689,19 +2689,19 @@
         <v>23</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="I5" s="2">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2724,19 +2724,19 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>94.7</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2756,19 +2756,19 @@
         <v>148</v>
       </c>
       <c r="E7">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1">
-        <v>93.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="H7" s="1">
-        <v>6.1</v>
+        <v>15.5</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2791,19 +2791,19 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>97</v>
+      </c>
+      <c r="H8" s="1">
         <v>3</v>
       </c>
-      <c r="G8" s="1">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="H8" s="1">
-        <v>9.1</v>
-      </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2826,19 +2826,19 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>85.7</v>
+        <v>90.5</v>
       </c>
       <c r="H9" s="1">
-        <v>14.3</v>
+        <v>9.5</v>
       </c>
       <c r="I9" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2861,19 +2861,19 @@
         <v>25</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>96</v>
+      </c>
+      <c r="H10" s="1">
         <v>4</v>
       </c>
-      <c r="G10" s="1">
-        <v>84</v>
-      </c>
-      <c r="H10" s="1">
-        <v>16</v>
-      </c>
       <c r="I10" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2896,19 +2896,19 @@
         <v>19</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>84.2</v>
+        <v>94.7</v>
       </c>
       <c r="H11" s="1">
-        <v>15.8</v>
+        <v>5.3</v>
       </c>
       <c r="I11" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2963,19 +2963,19 @@
         <v>119</v>
       </c>
       <c r="E13">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F13">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>88.2</v>
+        <v>95</v>
       </c>
       <c r="H13" s="1">
-        <v>11.8</v>
+        <v>5</v>
       </c>
       <c r="I13" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3010,7 +3010,7 @@
         <v>20.8</v>
       </c>
       <c r="I14" s="2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>36</v>
       </c>
       <c r="E15">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>88.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="H15" s="1">
-        <v>11.1</v>
+        <v>2.8</v>
       </c>
       <c r="I15" s="2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3068,19 +3068,19 @@
         <v>28</v>
       </c>
       <c r="E16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="I16" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3103,19 +3103,19 @@
         <v>35</v>
       </c>
       <c r="E17">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>88.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3138,19 +3138,19 @@
         <v>24</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>70.8</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>29.2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>2.7</v>
       </c>
       <c r="I19" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3205,19 +3205,19 @@
         <v>184</v>
       </c>
       <c r="E20">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="F20">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G20" s="1">
-        <v>87.5</v>
+        <v>95.7</v>
       </c>
       <c r="H20" s="1">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="I20" s="2">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3508,19 +3508,19 @@
         <v>663</v>
       </c>
       <c r="E29">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="F29">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G29" s="1">
-        <v>90.3</v>
+        <v>91.7</v>
       </c>
       <c r="H29" s="1">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I29" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>0</v>

--- a/academias/Lengua y Comunicación - Estadisticos 20241.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20241.xlsx
@@ -3307,16 +3307,16 @@
         <v>40</v>
       </c>
       <c r="E23">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23" s="1">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H23" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I23" s="2">
         <v>7.8</v>
@@ -3342,19 +3342,19 @@
         <v>41</v>
       </c>
       <c r="E24">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1">
-        <v>85.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="H24" s="1">
-        <v>14.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I24" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3377,16 +3377,16 @@
         <v>48</v>
       </c>
       <c r="E25">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="1">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="H25" s="1">
-        <v>6.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I25" s="2">
         <v>7.9</v>
@@ -3412,19 +3412,19 @@
         <v>36</v>
       </c>
       <c r="E26">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>94.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="H26" s="1">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="I26" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3447,19 +3447,19 @@
         <v>37</v>
       </c>
       <c r="E27">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3479,19 +3479,19 @@
         <v>202</v>
       </c>
       <c r="E28">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F28">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G28" s="1">
-        <v>91.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="I28" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3508,16 +3508,16 @@
         <v>663</v>
       </c>
       <c r="E29">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="F29">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G29" s="1">
-        <v>91.7</v>
+        <v>92.2</v>
       </c>
       <c r="H29" s="1">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I29" s="2">
         <v>8</v>
